--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -272,7 +272,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>PersonnePhysique</t>
@@ -322,10 +322,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Person.meta.id</t>
   </si>
   <si>
@@ -499,6 +506,12 @@
     <t>Meta.security</t>
   </si>
   <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
+  </si>
+  <si>
     <t>Person.meta.tag</t>
   </si>
   <si>
@@ -618,16 +631,10 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Person.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -649,10 +656,6 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la nationalité du professionel (Person).</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>paysNationalite</t>
   </si>
   <si>
@@ -1225,6 +1228,13 @@
     <t>An image that can be displayed as a thumbnail of the person to enhance the identification of the individual.</t>
   </si>
   <si>
+    <t>When providing a summary view (for example with Observation.value[x]) Attachment should be represented with a brief display text such as "Signed Procedure Consent".</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+att-1:If the Attachment has data, it SHALL have a contentType {data.empty() or contentType.exists()}</t>
+  </si>
+  <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/desc</t>
   </si>
   <si>
@@ -1244,7 +1254,14 @@
     <t>The organization that is the custodian of the person record.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>Need to know who recognizes this person record, manages and updates it.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>scoper</t>
@@ -1338,6 +1355,9 @@
   </si>
   <si>
     <t>Level of assurance that this link is associated with the target resource.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>The level of confidence that this link represents the same actual person, based on NIST Authentication Levels.</t>
@@ -1729,7 +1749,7 @@
     <col min="37" max="37" width="57.2265625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="78.4375" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="56.17578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="56.63671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2176,16 +2196,16 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM4" t="s" s="2">
         <v>77</v>
@@ -2196,10 +2216,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2222,13 +2242,13 @@
         <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2279,7 +2299,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2297,7 +2317,7 @@
         <v>77</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2308,14 +2328,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -2334,16 +2354,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2381,19 +2401,19 @@
         <v>77</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2402,16 +2422,16 @@
         <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2422,13 +2442,13 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>77</v>
@@ -2450,13 +2470,13 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2507,7 +2527,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2516,10 +2536,10 @@
         <v>79</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2536,10 +2556,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2565,13 +2585,13 @@
         <v>90</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2621,7 +2641,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2630,16 +2650,16 @@
         <v>88</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2650,10 +2670,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2676,16 +2696,16 @@
         <v>89</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2735,7 +2755,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2744,16 +2764,16 @@
         <v>88</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>77</v>
@@ -2764,10 +2784,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2790,16 +2810,16 @@
         <v>89</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2849,7 +2869,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2858,16 +2878,16 @@
         <v>88</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>77</v>
@@ -2878,10 +2898,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2904,16 +2924,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2963,7 +2983,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2972,16 +2992,16 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2992,10 +3012,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3018,16 +3038,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3053,13 +3073,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3077,7 +3097,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3086,30 +3106,30 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3132,16 +3152,16 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3167,13 +3187,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3191,7 +3211,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3200,30 +3220,30 @@
         <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>77</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3246,16 +3266,16 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3305,7 +3325,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3314,16 +3334,16 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3334,10 +3354,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3360,16 +3380,16 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3395,13 +3415,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3419,7 +3439,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3428,16 +3448,16 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3448,14 +3468,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3474,16 +3494,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3533,7 +3553,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3542,16 +3562,16 @@
         <v>88</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
@@ -3562,14 +3582,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3588,16 +3608,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3647,7 +3667,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3665,7 +3685,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3676,14 +3696,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3702,15 +3722,17 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3747,17 +3769,19 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="AC18" s="2"/>
+        <v>115</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>116</v>
+      </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3766,16 +3790,16 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3786,13 +3810,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3814,13 +3838,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3871,7 +3895,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3880,13 +3904,13 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
@@ -3900,13 +3924,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -3928,13 +3952,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3985,7 +4009,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3994,13 +4018,13 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>77</v>
@@ -4014,13 +4038,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4042,13 +4066,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4099,7 +4123,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4108,13 +4132,13 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>77</v>
@@ -4128,14 +4152,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4154,19 +4178,19 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4203,19 +4227,19 @@
         <v>77</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4224,16 +4248,16 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4244,10 +4268,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4270,17 +4294,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4329,7 +4353,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4338,30 +4362,30 @@
         <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4384,19 +4408,19 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4445,7 +4469,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4454,30 +4478,30 @@
         <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4500,13 +4524,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4557,7 +4581,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4575,7 +4599,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4586,14 +4610,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4612,16 +4636,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4659,19 +4683,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4683,13 +4707,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4700,13 +4724,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="B27" t="s" s="2">
-        <v>239</v>
-      </c>
       <c r="C27" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4728,13 +4752,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4785,7 +4809,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4797,7 +4821,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4814,10 +4838,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4840,19 +4864,19 @@
         <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4877,11 +4901,11 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4899,7 +4923,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4911,27 +4935,27 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4954,19 +4978,19 @@
         <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5015,7 +5039,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5027,31 +5051,31 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5070,16 +5094,16 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5129,7 +5153,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5141,31 +5165,31 @@
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5184,16 +5208,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5243,7 +5267,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5255,27 +5279,27 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5298,13 +5322,13 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5331,13 +5355,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5355,7 +5379,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5367,27 +5391,27 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5410,13 +5434,13 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5443,13 +5467,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5467,7 +5491,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5479,27 +5503,27 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5522,17 +5546,17 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5581,7 +5605,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5593,27 +5617,27 @@
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5636,19 +5660,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5697,7 +5721,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5706,30 +5730,30 @@
         <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5752,13 +5776,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5809,7 +5833,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5827,7 +5851,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -5838,14 +5862,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5864,16 +5888,16 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5911,19 +5935,19 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5935,13 +5959,13 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5952,13 +5976,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="C38" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -5980,13 +6004,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6037,7 +6061,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6049,7 +6073,7 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6066,10 +6090,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6092,13 +6116,13 @@
         <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6125,13 +6149,13 @@
         <v>77</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>77</v>
@@ -6149,7 +6173,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6158,30 +6182,30 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6204,19 +6228,19 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6265,7 +6289,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6277,27 +6301,27 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6320,19 +6344,19 @@
         <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6357,13 +6381,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -6381,7 +6405,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6393,27 +6417,27 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6436,16 +6460,16 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6495,7 +6519,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6507,27 +6531,27 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6550,13 +6574,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6607,7 +6631,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6619,27 +6643,27 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6662,19 +6686,19 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6699,13 +6723,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6723,7 +6747,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6732,30 +6756,30 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6778,19 +6802,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6839,7 +6863,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6848,30 +6872,30 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6894,19 +6918,19 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6955,7 +6979,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6964,30 +6988,30 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7010,15 +7034,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7067,7 +7093,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7076,30 +7102,30 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>391</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7122,17 +7148,19 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O48" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7181,7 +7209,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7190,16 +7218,16 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7210,10 +7238,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7236,17 +7264,17 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7295,7 +7323,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7304,19 +7332,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7324,10 +7352,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7350,13 +7378,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7395,17 +7423,17 @@
         <v>77</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7414,16 +7442,16 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7434,10 +7462,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7460,13 +7488,13 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7517,7 +7545,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7535,7 +7563,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7546,14 +7574,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7572,16 +7600,16 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7619,19 +7647,19 @@
         <v>77</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7640,16 +7668,16 @@
         <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7660,14 +7688,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7686,19 +7714,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7747,7 +7775,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7756,16 +7784,16 @@
         <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7776,10 +7804,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7802,15 +7830,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7859,7 +7889,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>88</v>
@@ -7868,16 +7898,16 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7888,10 +7918,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7914,15 +7944,17 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7947,13 +7979,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -7971,7 +8003,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7980,16 +8012,16 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8000,13 +8032,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>77</v>
@@ -8028,13 +8060,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8085,7 +8117,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8094,16 +8126,16 @@
         <v>79</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -8114,10 +8146,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8140,13 +8172,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8197,7 +8229,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8215,7 +8247,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -8226,14 +8258,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8252,16 +8284,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8299,19 +8331,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8320,16 +8352,16 @@
         <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8340,14 +8372,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8366,19 +8398,19 @@
         <v>89</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8427,7 +8459,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8436,16 +8468,16 @@
         <v>79</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8456,10 +8488,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8482,15 +8514,17 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8539,7 +8573,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>88</v>
@@ -8548,16 +8582,16 @@
         <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
@@ -8568,10 +8602,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8594,15 +8628,17 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>77</v>
@@ -8627,13 +8663,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8651,7 +8687,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8660,16 +8696,16 @@
         <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -579,7 +579,7 @@
     <t>Resource.language</t>
   </si>
   <si>
-    <t>langueParlee</t>
+    <t>PersonnePhysique.langueParlee</t>
   </si>
   <si>
     <t>Person.text</t>
@@ -656,7 +656,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la nationalité du professionel (Person).</t>
   </si>
   <si>
-    <t>paysNationalite</t>
+    <t>PersonnePhysique.paysNationalite</t>
   </si>
   <si>
     <t>Person.extension:as-ext-person-birth-place</t>
@@ -675,7 +675,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du lieu de naissance du professionnel en tant que personne physique.</t>
   </si>
   <si>
-    <t>lieuNaissance</t>
+    <t>PersonnePhysique.lieuNaissance</t>
   </si>
   <si>
     <t>Person.extension:as-ext-person-deceased-date-time</t>
@@ -694,7 +694,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la date de décès du professionnel (Date of death of the Person if applicable).</t>
   </si>
   <si>
-    <t>dateDeces</t>
+    <t>PersonnePhysique.dateDeces</t>
   </si>
   <si>
     <t>Person.modifierExtension</t>
@@ -858,7 +858,7 @@
     <t>HumanName.family</t>
   </si>
   <si>
-    <t>nomUsage</t>
+    <t>PersonnePhysique.nomUsage</t>
   </si>
   <si>
     <t>./part[partType = FAM]</t>
@@ -886,7 +886,7 @@
     <t>HumanName.given</t>
   </si>
   <si>
-    <t>prenomUsuel</t>
+    <t>PersonnePhysique.prenomUsuel</t>
   </si>
   <si>
     <t>./part[partType = GIV]</t>
@@ -913,7 +913,7 @@
     <t>HumanName.prefix</t>
   </si>
   <si>
-    <t>civilite</t>
+    <t>PersonnePhysique.civilite</t>
   </si>
   <si>
     <t>./part[partType = PFX]</t>
@@ -1153,7 +1153,7 @@
     <t>http://hl7.org/fhir/ValueSet/administrative-gender|4.0.1</t>
   </si>
   <si>
-    <t>sexeAdministratif</t>
+    <t>PersonnePhysique.sexeAdministratif</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1181,7 +1181,7 @@
     <t>Age of person drives many clinical processes, and is often used in performing identification of the person. Times are not included so as to not confuse things with potential timezone issues.</t>
   </si>
   <si>
-    <t>dateNaissance</t>
+    <t>PersonnePhysique.dateNaissance</t>
   </si>
   <si>
     <t>./birthTime</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-person.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
